--- a/data/2026-2027_zondag2.xlsx
+++ b/data/2026-2027_zondag2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Documents/Zondag 2 Team dashboard/sv-twello-zondag-2-dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpdh/Documents/Codex/2026-08-08/files-mentioned-by-the-user-overzicht/work/github-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7971DF7D-82C5-084D-A8CF-8E912EE78CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09E5E3A-2EFC-9142-B432-C1BC8D5236B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spelers" sheetId="1" r:id="rId1"/>
@@ -17175,7 +17175,7 @@
   <cols>
     <col min="2" max="2" width="16.5" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -17365,7 +17365,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -17532,7 +17532,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -17866,7 +17866,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -18033,7 +18033,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -18701,7 +18701,7 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -18868,7 +18868,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -20037,7 +20037,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -20204,7 +20204,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -20371,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -21373,7 +21373,7 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>0</v>
